--- a/daybook-generated-files/6.xlsx
+++ b/daybook-generated-files/6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\file\HV\Capital DayBook\11. NOV\XLSX File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\Shared Files\HV\Capital DayBook\2026\01. JAN\XLSX File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03A61FAB-028A-49F4-BFB9-2EE728972EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF40E294-3BA7-42CE-AB17-074162DE5672}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{6133993F-CB43-4397-A449-2F001F8F8456}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{E283EFA6-23D3-4E44-99A2-6C5DC4CD98BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Suspense Head Report" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
     <t>WESTERN RAILWAY</t>
   </si>
   <si>
-    <t>SUSPENSE HEAD   REPORT FROM 1/11/2025 TO 30/11/2025</t>
+    <t>SUSPENSE HEAD   REPORT FROM 1/1/2026 TO 31/1/2026</t>
   </si>
   <si>
     <t>Allocation Total</t>
@@ -426,7 +426,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EA780D0-5690-4C14-B909-66E65294A670}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F125C19-EB72-4358-AEE4-C1FEBA1DB571}">
   <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
